--- a/reports/Debug-snowbowl-20260105/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260105/For The Week Ending (Actual)_Visits.xlsx
@@ -37,10 +37,10 @@
     <t>Snowbowl Passes</t>
   </si>
   <si>
+    <t>Snowbowl Comp Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Comp Tickets</t>
   </si>
 </sst>
 </file>
@@ -448,7 +448,7 @@
         <v>46027</v>
       </c>
       <c r="C3" s="2">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -476,10 +476,10 @@
         <v>46027</v>
       </c>
       <c r="C5" s="2">
-        <v>550</v>
+        <v>368</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,10 +490,10 @@
         <v>46027</v>
       </c>
       <c r="C6" s="2">
-        <v>1826</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,7 +504,7 @@
         <v>46027</v>
       </c>
       <c r="C7" s="2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -518,7 +518,7 @@
         <v>46027</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -532,10 +532,10 @@
         <v>46027</v>
       </c>
       <c r="C9" s="2">
-        <v>368</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,7 +546,7 @@
         <v>46027</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>550</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>6</v>
@@ -560,10 +560,10 @@
         <v>46027</v>
       </c>
       <c r="C11" s="2">
-        <v>7</v>
+        <v>1826</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
